--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/1-Data-Model/DataTables.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/1-Data-Model/DataTables.xlsx
@@ -1549,9 +1549,9 @@
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="B48:C48"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B4:I4"/>
     <mergeCell ref="B32:G32"/>
     <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B4:I4"/>
     <mergeCell ref="B37:I37"/>
     <mergeCell ref="B13:F13"/>
   </mergeCells>
@@ -1566,7 +1566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I65"/>
+  <dimension ref="B2:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -2255,17 +2255,200 @@
         </is>
       </c>
     </row>
+    <row r="67" ht="16.5" customHeight="1">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>A transposed data table keeps both keys: "_PK_" in the first row and "&gt;table" in the column next to the field names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Data Employee managers</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="n"/>
+      <c r="D69" s="9" t="n"/>
+      <c r="E69" s="9" t="n"/>
+      <c r="F69" s="7" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>_PK_</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n"/>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n"/>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>Eve</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Finn</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>&gt;stores</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n"/>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Method String ManagerCity(Integer index)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>return managers[index].store.city;</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Test ManagerCity ManagerCityTest</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="n"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>_res_</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="16">
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B21:I21"/>
     <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="B44:C44"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B69:F69"/>
     <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B78:C78"/>
     <mergeCell ref="B38:I38"/>
     <mergeCell ref="B51:I51"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B67:I67"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B62:G62"/>
     <mergeCell ref="B53:C53"/>

--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/1-Data-Model/DataTables.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/1-Data-Model/DataTables.xlsx
@@ -932,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I52"/>
+  <dimension ref="B2:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1480,79 +1480,98 @@
     <row r="45">
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Method String SeasonalName(Integer index)</t>
-        </is>
-      </c>
+          <t>Spreadsheet String SeasonalName(Integer index)</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>return seasonalProducts[index].name;</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>= seasonalProducts[index].name</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Test SeasonalName SeasonalNameTest</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="4" t="inlineStr">
+      <c r="C49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t>Pumpkin</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Pumpkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>Watermelon</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B21:I21"/>
-    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B32:G32"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B49:C49"/>
     <mergeCell ref="B13:F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1566,7 +1585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I82"/>
+  <dimension ref="B2:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -2372,71 +2391,89 @@
     <row r="75">
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Method String ManagerCity(Integer index)</t>
-        </is>
-      </c>
+          <t>Spreadsheet String ManagerCity(Integer index)</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>return managers[index].store.city;</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>= managers[index].store.city</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>Test ManagerCity ManagerCityTest</t>
         </is>
       </c>
-      <c r="C78" s="7" t="n"/>
-    </row>
-    <row r="79">
-      <c r="B79" s="4" t="inlineStr">
+      <c r="C79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="B80" s="5" t="inlineStr">
+    <row r="81">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>City</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>Denver</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C82" s="10" t="inlineStr">
+      <c r="C83" s="10" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="B21:I21"/>
@@ -2444,15 +2481,16 @@
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B78:C78"/>
     <mergeCell ref="B38:I38"/>
     <mergeCell ref="B51:I51"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B67:I67"/>
     <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B79:C79"/>
     <mergeCell ref="B62:G62"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B75:C75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
